--- a/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
+++ b/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
   <si>
     <t>SR#</t>
   </si>
@@ -180,6 +180,113 @@
 View Recorded Beneficiary section
 Validation and error messages
 Ensured all labels, placeholders, buttons, and validation messages dynamically switch based on the selected language.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">week off </t>
+  </si>
+  <si>
+    <t>16th feb</t>
+  </si>
+  <si>
+    <t>Harpriya</t>
+  </si>
+  <si>
+    <t>work done on the Product Section, leading to a complete redesign with a clear separation between Product-Based and Shop-Based workflows. Dynamic visibility logic was implemented to display only relevant fields, providing a streamlined and intuitive experience while ensuring accurate data capture across both workflow types.
+All new fields were developed and integrated, including dependent dropdowns, multi-select options, and conditional inputs. Robust state management was applied to handle real-time user input, ensuring consistency and reliability in data entry.
+Frontend interactions were engineered to guarantee smooth rendering and seamless toggling between product-based and shop-based workflows. Live validation feedback and consistent data binding enhanced usability and maintained a high-quality user experience.
+Thorough testing and debugging of the entire section were conducted, verifying field behaviors and conditional logic. Performance optimizations minimized re-renders and ensured stable, efficient, and reliable operation of the form under various use cases.</t>
+  </si>
+  <si>
+    <t>17th feb</t>
+  </si>
+  <si>
+    <t>Worked on CRP-EP App- Product Section Redesign and Segmentation: Led the complete redesign of the product section with clear separation between Product-Based and Shop-Based workflows, implementing dynamic visibility logic. Ensured accurate data capture and streamlined user experience for both workflow types.
+Field Architecture and Dynamic Form Implementation: Developed all new fields including dependent dropdowns, multi-selects, and conditional inputs with robust state management. Supported real-time user input.
+Frontend Functionality: Made responsive frontend interactions to ensure smooth rendering and seamless toggling between product-based and shop-based options. Maintained consistent data binding and live validation feedback for optimal UX.
+Testing, Debugging, and Performance Optimization: Conducted thorough  testing for field behaviors and conditional logic. Optimized performance, minimized re-renders, and ensured stable and efficient form operations.</t>
+  </si>
+  <si>
+    <t>Worked on CRP-EP App- Got the Shop Section reviewed and approved by the management team after incorporating the required structural and workflow changes.
+Received updated APIs and revised API structure for the complete forms from the backend team, including changes in the /existing-enterprise/ flow and related modules such as license, subsidy (7 details), enterprise shop, enterprise shop media, enterprise product, product media, and enterprise media.
+Also received and reviewed shared APIs including enterprise types, enterprise support, mandatory funds, enterprise training (received &amp; required), training certificates, and recorded beneficiary modules to understand the updated data structure.
+Started working on aligning and mapping frontend fields with the updated API structure, modifying the previous data storage and submission flow to match the new backend response and request formats.
+Worked specifically on the Enterprise License API for the Existing Enterprise form; encountered a roadblock where the API was not sending data successfully due to missing/incorrect field mappings in the payload.
+Debugged the issue by tracing the request structure, identifying missing fields in the API payload, and refactoring the code accordingly to ensure proper data transmission and successful API integration.</t>
+  </si>
+  <si>
+    <t>Got the Shop Section approved by the management team after implementing the required workflow and structural changes. Received the updated APIs and revised API structure from the backend team for both forms, including /existing-enterprise/ and related modules such as license, subsidy (7 details), enterprise shop, enterprise shop media, enterprise product, product media, enterprise media, and other shared APIs like enterprise types, enterprise support, mandatory funds, enterprise training (received &amp; required), training certificates, and recorded beneficiary. Started working on mapping the frontend fields with the updated API structure and modified the previous data storage and submission flow according to the new request/response format. While integrating the Enterprise License API for the existing form, faced an issue where data was not being sent successfully due to missing fields in the payload. Debugged the code, identified the incorrect field mappings, and refactored the implementation to ensure proper data transmission and API integration.</t>
+  </si>
+  <si>
+    <t>18th feb</t>
+  </si>
+  <si>
+    <t>Worked on crp-ep app- Worked on the complete Loan Details and Subsidy Details sections, restructuring the API data storage flow as per the updated backend requirements.
+Implemented conditional logic for the Loan section including fields such as Is Loan Taken (Yes/No), Institution Name, Bank Loan Details, Branch Name, Loan Amount, Repaid Amount, and Repayment Status.
+Ensured proper field validation, accurate payload formation, and correct mapping of all loan-related data before API submission to guarantee successful backend storage.
+Structured the Subsidy section with fields including Is Subsidy Taken (Yes/No), Institution Name, and Subsidy Description, aligning it with the revised API format.
+Verified end-to-end data flow to ensure all loan and subsidy details are correctly validated, synchronized, and stored in the backend without data loss.</t>
+  </si>
+  <si>
+    <t>Worked on the Loan and Subsidy Details sections by updating the API flow according to the new backend structure and required fields. Added conditional logic and validation for loan-related fields such as Loan Taken (Yes/No), institution name, bank details, branch name, loan amount, repaid amount, and repayment status to ensure correct data entry and proper submission.
+Also implemented the Subsidy section with fields like Subsidy Taken (Yes/No), institution name, and description, making sure all details are properly validated, mapped, and stored in the backend as per the updated API format.</t>
+  </si>
+  <si>
+    <t>19th feb</t>
+  </si>
+  <si>
+    <t>Worked on CRP-EP App-Worked on the Enterprise Shop section, aligning frontend fields with the updated API structure and ensuring data is correctly sent and mapped to the appropriate backend fields.
+Implemented and integrated the Enterprise Media fields, ensuring proper file handling and accurate API data submission as per the revised backend format.
+Modified the entire Enterprise Product section according to the updated API, including proper mapping and submission of all product-related fields along with media attachments.
+Worked on the Cadre and Cadre Designation fields, ensuring correct field mapping and successful data transmission to the backend through the updated API structure.</t>
+  </si>
+  <si>
+    <t>Worked on the Enterprise Shop section by updating the API integration and ensuring that all frontend fields are properly mapped and sent to the correct backend fields as per the revised API structure. Also implemented the Enterprise Media fields, handling file uploads and ensuring accurate data submission according to the updated backend format.
+Additionally, modified the entire Enterprise Product section to align with the updated APIs, including proper mapping of all product-related fields and media attachments. Worked on the Cadre and Cadre Designation fields as well, ensuring correct data transmission and successful API submission based on the new structure.</t>
+  </si>
+  <si>
+    <t>20th feb</t>
+  </si>
+  <si>
+    <t>Worked on CRP-EP App-Worked on the shared APIs including Enterprise Type, Enterprise Support, and the complete Funds section, aligning all fields with the updated API structure.
+Handled the entire Training Received and Training Required sections, ensuring proper field mapping and data submission according to the new workflow.
+Ensured correct integration and updating of Training Certificates as per the revised API format and backend requirements.
+Verified proper validation and smooth data flow across all shared modules based on the updated API workflow.</t>
+  </si>
+  <si>
+    <t>Worked extensively on the shared APIs, including Enterprise Type, Enterprise Support, and the complete Funds section, ensuring all fields were properly aligned with the updated API structure and new workflow requirements. Updated the field mappings and submission logic so that data is accurately sent and stored in the backend according to the revised flow.
+Handled the entire Training section, covering both Training Received and Training Required modules, implementing all related fields and ensuring proper validation, conditional handling, and correct payload formation before API submission. Additionally, worked on the integration and updating process of Training Certificates, making sure certificate data is correctly uploaded, mapped, and synchronized with the backend as per the new API workflow. Ensured smooth end-to-end data flow and consistency across all shared modules after the API changes.</t>
+  </si>
+  <si>
+    <t>21st feb</t>
+  </si>
+  <si>
+    <t>Worked on CRP_EP APP-Worked on updating the Recorded Beneficiary module as per the revised API structure and workflow changes.
+Faced certain bugs and roadblocks during integration, identified the issues in data mapping and API responses, and resolved them to ensure smooth functionality.
+Worked on the View Recorded Form section for both the No Enterprise Form and the New Enterprise Form, ensuring all recorded data is properly displayed.
+Ensured that all 9–10 sections of the Existing Enterprise form and the complete New Enterprise form are accurately rendered in the view mode with all updated fields.
+Verified the end-to-end data flow based on the updated and modified API structure to ensure complete and correct data visibility in the recorded view.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weekoff Sunday </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRP-EP </t>
+  </si>
+  <si>
+    <t>Worked on updating the Recorded Beneficiary module according to the revised and updated API structure. During the integration process, encountered certain bugs and roadblocks related to data mapping and API response handling, which were identified and resolved to ensure smooth and accurate functionality.
+Also worked extensively on the View Recorded Form section for both the No Enterprise form and the New Enterprise form. Ensured that all recorded data is properly fetched and displayed in view mode, covering all 9–10 sections of the Existing Enterprise form as well as the complete New Enterprise form. Verified that every field, including newly added and modified fields, is correctly rendered based on the updated API flow. Ensured proper end-to-end data synchronization so that the recorded data reflects accurately and completely in the frontend as per the latest backend changes.</t>
+  </si>
+  <si>
+    <t>Worked on the CRP-EP App-  matched and align all fields displayed in the View Recorded section with the updated form structure and API flow.
+Identified and added missing fields in the View Recorded module to ensure complete and accurate data visibility.
+Raised and documented a total of 3 change requests based on development flow requirements, including adding the New Enterprise form, adding the No Enterprise form, and later removing the No Enterprise form as per updated requirements.</t>
+  </si>
+  <si>
+    <t>worked on- the fields displayed in the View Recorded section were properly aligned with the latest form structure and updated API flow. Reviewed the recorded view carefully, identified missing or mismatched fields, and updated the implementation to ensure complete and accurate data display.
+During the development process, initiated and worked on three change requests based on evolving requirements. These included introducing the New Enterprise form, implementing the No Enterprise form, and subsequently removing the No Enterprise form as per revised project direction.</t>
+  </si>
+  <si>
+    <t>23rd feb</t>
   </si>
 </sst>
 </file>
@@ -230,7 +337,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -253,11 +360,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -284,6 +431,31 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,15 +737,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="2" max="2" width="73.5546875" customWidth="1"/>
     <col min="3" max="3" width="16.44140625" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.33203125" customWidth="1"/>
+    <col min="7" max="7" width="70.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -855,7 +1027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -878,10 +1050,213 @@
         <v>43</v>
       </c>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
+++ b/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kavya\Desktop\TH-PROJECT-NOTEBOOK\MPR\Role wise\Technical Support\Feb'26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\TH-PROJECT-NOTEBOOK\MPR\Role wise\Technical Support\Feb'26\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7D2058-3813-4BD6-8F0A-26D314C9F53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feb 2026" sheetId="1" r:id="rId1"/>
@@ -19,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
   <si>
     <t>SR#</t>
   </si>
@@ -260,21 +252,10 @@
     <t>21st feb</t>
   </si>
   <si>
-    <t>Worked on CRP_EP APP-Worked on updating the Recorded Beneficiary module as per the revised API structure and workflow changes.
-Faced certain bugs and roadblocks during integration, identified the issues in data mapping and API responses, and resolved them to ensure smooth functionality.
-Worked on the View Recorded Form section for both the No Enterprise Form and the New Enterprise Form, ensuring all recorded data is properly displayed.
-Ensured that all 9–10 sections of the Existing Enterprise form and the complete New Enterprise form are accurately rendered in the view mode with all updated fields.
-Verified the end-to-end data flow based on the updated and modified API structure to ensure complete and correct data visibility in the recorded view.</t>
-  </si>
-  <si>
     <t xml:space="preserve">weekoff Sunday </t>
   </si>
   <si>
     <t xml:space="preserve">CRP-EP </t>
-  </si>
-  <si>
-    <t>Worked on updating the Recorded Beneficiary module according to the revised and updated API structure. During the integration process, encountered certain bugs and roadblocks related to data mapping and API response handling, which were identified and resolved to ensure smooth and accurate functionality.
-Also worked extensively on the View Recorded Form section for both the No Enterprise form and the New Enterprise form. Ensured that all recorded data is properly fetched and displayed in view mode, covering all 9–10 sections of the Existing Enterprise form as well as the complete New Enterprise form. Verified that every field, including newly added and modified fields, is correctly rendered based on the updated API flow. Ensured proper end-to-end data synchronization so that the recorded data reflects accurately and completely in the frontend as per the latest backend changes.</t>
   </si>
   <si>
     <t>Worked on the CRP-EP App-  matched and align all fields displayed in the View Recorded section with the updated form structure and API flow.
@@ -287,12 +268,26 @@
   </si>
   <si>
     <t>23rd feb</t>
+  </si>
+  <si>
+    <t>Worked on CRP_EP APP-Worked on updating the Recorded Beneficiary module as per the revised API structure and workflow changes.
+Faced certain bugs and roadblocks during integration, identified the issues in data mapping and API responses, and resolved them to ensure smooth functionality.
+Worked on the View Recorded Form section for Existing Enterprise Form, ensuring all recorded data is properly displayed.
+Ensured that all 9–10 sections of the Complete Existing Enterprise form are accurately rendered in the view mode with all updated fields.
+Verified the end-to-end data flow based on the updated and modified API structure to ensure complete and correct data visibility in the recorded view.</t>
+  </si>
+  <si>
+    <t>Worked on updating the Recorded Beneficiary module according to the revised and updated API structure. During the integration process, encountered certain bugs and roadblocks related to data mapping and API response handling, which were identified and resolved to ensure smooth and accurate functionality.
+Also worked extensively on the View Recorded Form section for both the No Enterprise form and the New Enterprise form. Ensured that all recorded data is properly fetched and displayed in view mode, covering all 9–10 sections of the Existing Enterprise form. Verified that every field, including newly added and modified fields, is correctly rendered based on the updated API flow. Ensured proper end-to-end data synchronization so that the recorded data reflects accurately and completely in the frontend as per the latest backend changes.</t>
+  </si>
+  <si>
+    <t>Compensatory leave due to office work on Sunday (08-02-26)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -404,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -422,40 +417,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -736,19 +718,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="73.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.33203125" customWidth="1"/>
+    <col min="2" max="2" width="73.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -771,20 +753,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-    </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -807,7 +789,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -830,7 +812,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -853,7 +835,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -876,24 +858,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -912,11 +894,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -935,11 +917,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -958,11 +940,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -981,54 +963,54 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+    <row r="13" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+    <row r="14" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1037,70 +1019,70 @@
       <c r="C14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="11">
-        <v>15</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-    </row>
-    <row r="17" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="1:7" ht="255" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
+    <row r="18" spans="1:7" ht="300" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1109,21 +1091,21 @@
       <c r="C18" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="11">
+    <row r="19" spans="1:7" ht="210" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -1132,21 +1114,21 @@
       <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E19" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="11">
+    <row r="20" spans="1:7" ht="165" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1155,21 +1137,21 @@
       <c r="C20" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E20" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
+    <row r="21" spans="1:7" ht="195" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1178,76 +1160,76 @@
       <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E21" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
+    <row r="22" spans="1:7" ht="195" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E22" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="11">
-        <v>22</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="24" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
+++ b/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\TH-PROJECT-NOTEBOOK\MPR\Role wise\Technical Support\Feb'26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kavya\Desktop\TH-PROJECT-NOTEBOOK\MPR\Role wise\Technical Support\Feb'26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7D2058-3813-4BD6-8F0A-26D314C9F53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="Feb 2026" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
   <si>
     <t>SR#</t>
   </si>
@@ -183,30 +182,7 @@
     <t>Harpriya</t>
   </si>
   <si>
-    <t>work done on the Product Section, leading to a complete redesign with a clear separation between Product-Based and Shop-Based workflows. Dynamic visibility logic was implemented to display only relevant fields, providing a streamlined and intuitive experience while ensuring accurate data capture across both workflow types.
-All new fields were developed and integrated, including dependent dropdowns, multi-select options, and conditional inputs. Robust state management was applied to handle real-time user input, ensuring consistency and reliability in data entry.
-Frontend interactions were engineered to guarantee smooth rendering and seamless toggling between product-based and shop-based workflows. Live validation feedback and consistent data binding enhanced usability and maintained a high-quality user experience.
-Thorough testing and debugging of the entire section were conducted, verifying field behaviors and conditional logic. Performance optimizations minimized re-renders and ensured stable, efficient, and reliable operation of the form under various use cases.</t>
-  </si>
-  <si>
     <t>17th feb</t>
-  </si>
-  <si>
-    <t>Worked on CRP-EP App- Product Section Redesign and Segmentation: Led the complete redesign of the product section with clear separation between Product-Based and Shop-Based workflows, implementing dynamic visibility logic. Ensured accurate data capture and streamlined user experience for both workflow types.
-Field Architecture and Dynamic Form Implementation: Developed all new fields including dependent dropdowns, multi-selects, and conditional inputs with robust state management. Supported real-time user input.
-Frontend Functionality: Made responsive frontend interactions to ensure smooth rendering and seamless toggling between product-based and shop-based options. Maintained consistent data binding and live validation feedback for optimal UX.
-Testing, Debugging, and Performance Optimization: Conducted thorough  testing for field behaviors and conditional logic. Optimized performance, minimized re-renders, and ensured stable and efficient form operations.</t>
-  </si>
-  <si>
-    <t>Worked on CRP-EP App- Got the Shop Section reviewed and approved by the management team after incorporating the required structural and workflow changes.
-Received updated APIs and revised API structure for the complete forms from the backend team, including changes in the /existing-enterprise/ flow and related modules such as license, subsidy (7 details), enterprise shop, enterprise shop media, enterprise product, product media, and enterprise media.
-Also received and reviewed shared APIs including enterprise types, enterprise support, mandatory funds, enterprise training (received &amp; required), training certificates, and recorded beneficiary modules to understand the updated data structure.
-Started working on aligning and mapping frontend fields with the updated API structure, modifying the previous data storage and submission flow to match the new backend response and request formats.
-Worked specifically on the Enterprise License API for the Existing Enterprise form; encountered a roadblock where the API was not sending data successfully due to missing/incorrect field mappings in the payload.
-Debugged the issue by tracing the request structure, identifying missing fields in the API payload, and refactoring the code accordingly to ensure proper data transmission and successful API integration.</t>
-  </si>
-  <si>
-    <t>Got the Shop Section approved by the management team after implementing the required workflow and structural changes. Received the updated APIs and revised API structure from the backend team for both forms, including /existing-enterprise/ and related modules such as license, subsidy (7 details), enterprise shop, enterprise shop media, enterprise product, product media, enterprise media, and other shared APIs like enterprise types, enterprise support, mandatory funds, enterprise training (received &amp; required), training certificates, and recorded beneficiary. Started working on mapping the frontend fields with the updated API structure and modified the previous data storage and submission flow according to the new request/response format. While integrating the Enterprise License API for the existing form, faced an issue where data was not being sent successfully due to missing fields in the payload. Debugged the code, identified the incorrect field mappings, and refactored the implementation to ensure proper data transmission and API integration.</t>
   </si>
   <si>
     <t>18th feb</t>
@@ -239,16 +215,6 @@
     <t>20th feb</t>
   </si>
   <si>
-    <t>Worked on CRP-EP App-Worked on the shared APIs including Enterprise Type, Enterprise Support, and the complete Funds section, aligning all fields with the updated API structure.
-Handled the entire Training Received and Training Required sections, ensuring proper field mapping and data submission according to the new workflow.
-Ensured correct integration and updating of Training Certificates as per the revised API format and backend requirements.
-Verified proper validation and smooth data flow across all shared modules based on the updated API workflow.</t>
-  </si>
-  <si>
-    <t>Worked extensively on the shared APIs, including Enterprise Type, Enterprise Support, and the complete Funds section, ensuring all fields were properly aligned with the updated API structure and new workflow requirements. Updated the field mappings and submission logic so that data is accurately sent and stored in the backend according to the revised flow.
-Handled the entire Training section, covering both Training Received and Training Required modules, implementing all related fields and ensuring proper validation, conditional handling, and correct payload formation before API submission. Additionally, worked on the integration and updating process of Training Certificates, making sure certificate data is correctly uploaded, mapped, and synchronized with the backend as per the new API workflow. Ensured smooth end-to-end data flow and consistency across all shared modules after the API changes.</t>
-  </si>
-  <si>
     <t>21st feb</t>
   </si>
   <si>
@@ -256,11 +222,6 @@
   </si>
   <si>
     <t xml:space="preserve">CRP-EP </t>
-  </si>
-  <si>
-    <t>Worked on the CRP-EP App-  matched and align all fields displayed in the View Recorded section with the updated form structure and API flow.
-Identified and added missing fields in the View Recorded module to ensure complete and accurate data visibility.
-Raised and documented a total of 3 change requests based on development flow requirements, including adding the New Enterprise form, adding the No Enterprise form, and later removing the No Enterprise form as per updated requirements.</t>
   </si>
   <si>
     <t>worked on- the fields displayed in the View Recorded section were properly aligned with the latest form structure and updated API flow. Reviewed the recorded view carefully, identified missing or mismatched fields, and updated the implementation to ensure complete and accurate data display.
@@ -270,24 +231,106 @@
     <t>23rd feb</t>
   </si>
   <si>
-    <t>Worked on CRP_EP APP-Worked on updating the Recorded Beneficiary module as per the revised API structure and workflow changes.
-Faced certain bugs and roadblocks during integration, identified the issues in data mapping and API responses, and resolved them to ensure smooth functionality.
-Worked on the View Recorded Form section for Existing Enterprise Form, ensuring all recorded data is properly displayed.
-Ensured that all 9–10 sections of the Complete Existing Enterprise form are accurately rendered in the view mode with all updated fields.
-Verified the end-to-end data flow based on the updated and modified API structure to ensure complete and correct data visibility in the recorded view.</t>
-  </si>
-  <si>
-    <t>Worked on updating the Recorded Beneficiary module according to the revised and updated API structure. During the integration process, encountered certain bugs and roadblocks related to data mapping and API response handling, which were identified and resolved to ensure smooth and accurate functionality.
-Also worked extensively on the View Recorded Form section for both the No Enterprise form and the New Enterprise form. Ensured that all recorded data is properly fetched and displayed in view mode, covering all 9–10 sections of the Existing Enterprise form. Verified that every field, including newly added and modified fields, is correctly rendered based on the updated API flow. Ensured proper end-to-end data synchronization so that the recorded data reflects accurately and completely in the frontend as per the latest backend changes.</t>
-  </si>
-  <si>
     <t>Compensatory leave due to office work on Sunday (08-02-26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked on TMS home page UI along with responsoveness </t>
+  </si>
+  <si>
+    <t>competed</t>
+  </si>
+  <si>
+    <t>24th feb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25th feb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">worked on the header section and its pages and subpages </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26th feb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">worked on the header section and its pages and subpages LDMS, enterprise tracking, monitoring &amp; analysis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27th feb </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> header section suboptions- Dashboard - suboptions ,Resource centre suboptions, login button UI along with responsiveness </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28th feb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard  UI part added graph chart for the analytics  and worked on the card UI along with daashboard structure </t>
+  </si>
+  <si>
+    <t>Worked on the TMS, including the header section, the About Us page and its subpages, the Our Services section and its subpages, Beneficiary Profiling, and User Management, while also improving their responsiveness.</t>
+  </si>
+  <si>
+    <t>Worked on TMS, focusing on the header section options including LDMS, Enterprise Tracking, and Monitoring &amp; Analysis.</t>
+  </si>
+  <si>
+    <t>Worked on TMS, including the header section sub-options such as Dashboard (with its sub-options), Resource Centre sub-options, and the Login button UI, along with improving responsiveness</t>
+  </si>
+  <si>
+    <t>Worked on the TMS Dashboard UI by adding graph charts for analytics, designing card components, and improving the overall dashboard structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked on the UI part of the TMS home page including all the homepage sections </t>
+  </si>
+  <si>
+    <t>Worked on the CRP-EP App by aligning all fields in the View Recorded section with the updated form structure and API flow.
+Added missing fields in the View Recorded module to ensure complete data visibility.
+Raised and documented 3 change requests: adding the New Enterprise form, adding the No Enterprise form, and later removing the No Enterprise form as per updated requirements</t>
+  </si>
+  <si>
+    <t>Worked on the CRP-EP App by updating the Recorded Beneficiary module as per the revised API structure and workflow changes, and resolving bugs related to data mapping and API responses.
+Also worked on the View Recorded Form for the Existing Enterprise form, ensuring all sections and updated fields display correctly with proper end-to-end data flow.</t>
+  </si>
+  <si>
+    <t>Updated the Recorded Beneficiary module as per the revised API structure, identifying and resolving issues related to data mapping and API responses during integration.
+Also worked on the View Recorded Form for No Enterprise and New Enterprise forms, ensuring all sections and fields display correctly with proper end-to-end data flow.</t>
+  </si>
+  <si>
+    <t>Worked on the CRP-EP App by integrating shared APIs for Enterprise Type, Enterprise Support, Funds, and the Training sections, aligning all fields with the updated API structure.
+Ensured proper field mapping, validation, and smooth data flow, including correct integration of Training Certificates as per the revised API workflow.</t>
+  </si>
+  <si>
+    <t>Worked on the CRP-EP App by getting the Shop section reviewed and approved after incorporating required structural and workflow changes.
+Reviewed updated APIs for Existing Enterprise modules including license, subsidy, shop, product, media, and related sections.
+Started aligning frontend fields with the revised API structure and modified the previous data submission flow accordingly.
+Debugged and resolved issues in the Enterprise License API by fixing missing field mappings in the payload to ensure successful integration.</t>
+  </si>
+  <si>
+    <t>Got the Shop Section approved after implementing the required workflow and structural changes, and reviewed updated APIs for Existing Enterprise and related modules.
+Started mapping frontend fields with the revised API structure and resolved payload issues while integrating the Enterprise License API to ensure proper data transmission.</t>
+  </si>
+  <si>
+    <t>Worked on shared APIs including Enterprise Type, Enterprise Support, and the Funds section, aligning all fields with the updated API structure and workflow.
+Updated field mappings and submission logic to ensure accurate data storage in the backend.
+Handled the Training section (Training Received and Training Required) with conditional handling, and payload formation.
+Integrated Training Certificates and ensured smooth end-to-end data flow across all modules as per the revised API workflow.</t>
+  </si>
+  <si>
+    <t>Redesigned the Product Section in the CRP-EP App by separating Product-Based and Shop-Based workflows with dynamic visibility and improved user experience.
+Implemented new fields with dependent dropdowns, multi-selects, conditional inputs, and proper state management with live validation.
+Developed responsive frontend interactions ensuring smooth toggling, consistent data binding, and seamless rendering.
+Performed thorough testing, debugging, and performance optimization to ensure stable and efficient form operations.</t>
+  </si>
+  <si>
+    <t>Redesigned the Product Section with a clear separation between Product-Based and Shop-Based workflows, implementing dynamic visibility for relevant fields.
+Developed and integrated new fields including dependent dropdowns, multi-selects, and conditional inputs with proper state management.
+Implemented smooth frontend interactions with live validation and consistent data binding for better user experience.
+Conducted thorough testing, debugging, and performance optimization to ensure stable and efficient form functionality.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -399,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -418,6 +461,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -436,9 +482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,19 +762,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="73.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.28515625" customWidth="1"/>
+    <col min="2" max="2" width="73.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -753,20 +797,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -789,7 +833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -812,7 +856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -835,7 +879,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -858,20 +902,20 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -894,7 +938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -917,7 +961,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -940,7 +984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -963,7 +1007,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -986,7 +1030,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1009,7 +1053,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -1032,38 +1076,38 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" ht="255" x14ac:dyDescent="0.25">
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>49</v>
+      <c r="B17" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -1078,15 +1122,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="300" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -1095,21 +1139,21 @@
         <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="210" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -1118,21 +1162,21 @@
         <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="165" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -1141,21 +1185,21 @@
         <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="195" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -1164,21 +1208,21 @@
         <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="195" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -1187,49 +1231,164 @@
         <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="15">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="15">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="15">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="15">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="15">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
+++ b/MPR/Role wise/Technical Support/Feb'26/Individual_MPR (Haripriya).xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
   <si>
     <t>SR#</t>
   </si>
@@ -74,27 +74,15 @@
     <t>5th feb</t>
   </si>
   <si>
-    <t>4th feb</t>
-  </si>
-  <si>
     <t xml:space="preserve">TMS </t>
   </si>
   <si>
     <t>10th feb</t>
   </si>
   <si>
-    <t xml:space="preserve">7th feb </t>
-  </si>
-  <si>
     <t xml:space="preserve">worked on contact person creation &amp; updation  and validations in the field </t>
   </si>
   <si>
-    <t xml:space="preserve">8th feb </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9th feb </t>
-  </si>
-  <si>
     <t xml:space="preserve">On leave due to personal reasons </t>
   </si>
   <si>
@@ -117,9 +105,6 @@
   </si>
   <si>
     <t>Worked on CRP-EP App- Worked on the CRP EP app to analyze fields whose data is not being recorded in the backend database, and identified new fields that need to be added to the backend.</t>
-  </si>
-  <si>
-    <t>12th feb</t>
   </si>
   <si>
     <t>Implemented language conversion in the Existing Form module, covering the Investment Details section and the Loan &amp; Subsidy Details section, including all related loan and subsidy components.</t>
@@ -176,16 +161,7 @@
     <t xml:space="preserve">week off </t>
   </si>
   <si>
-    <t>16th feb</t>
-  </si>
-  <si>
     <t>Harpriya</t>
-  </si>
-  <si>
-    <t>17th feb</t>
-  </si>
-  <si>
-    <t>18th feb</t>
   </si>
   <si>
     <t>Worked on crp-ep app- Worked on the complete Loan Details and Subsidy Details sections, restructuring the API data storage flow as per the updated backend requirements.
@@ -199,9 +175,6 @@
 Also implemented the Subsidy section with fields like Subsidy Taken (Yes/No), institution name, and description, making sure all details are properly validated, mapped, and stored in the backend as per the updated API format.</t>
   </si>
   <si>
-    <t>19th feb</t>
-  </si>
-  <si>
     <t>Worked on CRP-EP App-Worked on the Enterprise Shop section, aligning frontend fields with the updated API structure and ensuring data is correctly sent and mapped to the appropriate backend fields.
 Implemented and integrated the Enterprise Media fields, ensuring proper file handling and accurate API data submission as per the revised backend format.
 Modified the entire Enterprise Product section according to the updated API, including proper mapping and submission of all product-related fields along with media attachments.
@@ -212,12 +185,6 @@
 Additionally, modified the entire Enterprise Product section to align with the updated APIs, including proper mapping of all product-related fields and media attachments. Worked on the Cadre and Cadre Designation fields as well, ensuring correct data transmission and successful API submission based on the new structure.</t>
   </si>
   <si>
-    <t>20th feb</t>
-  </si>
-  <si>
-    <t>21st feb</t>
-  </si>
-  <si>
     <t xml:space="preserve">weekoff Sunday </t>
   </si>
   <si>
@@ -234,30 +201,15 @@
     <t>Compensatory leave due to office work on Sunday (08-02-26)</t>
   </si>
   <si>
-    <t xml:space="preserve">Worked on TMS home page UI along with responsoveness </t>
-  </si>
-  <si>
     <t>competed</t>
   </si>
   <si>
-    <t>24th feb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25th feb </t>
-  </si>
-  <si>
     <t xml:space="preserve">worked on the header section and its pages and subpages </t>
   </si>
   <si>
-    <t xml:space="preserve">26th feb </t>
-  </si>
-  <si>
     <t xml:space="preserve">worked on the header section and its pages and subpages LDMS, enterprise tracking, monitoring &amp; analysis </t>
   </si>
   <si>
-    <t xml:space="preserve">27th feb </t>
-  </si>
-  <si>
     <t xml:space="preserve"> header section suboptions- Dashboard - suboptions ,Resource centre suboptions, login button UI along with responsiveness </t>
   </si>
   <si>
@@ -265,18 +217,6 @@
   </si>
   <si>
     <t xml:space="preserve">Dashboard  UI part added graph chart for the analytics  and worked on the card UI along with daashboard structure </t>
-  </si>
-  <si>
-    <t>Worked on the TMS, including the header section, the About Us page and its subpages, the Our Services section and its subpages, Beneficiary Profiling, and User Management, while also improving their responsiveness.</t>
-  </si>
-  <si>
-    <t>Worked on TMS, focusing on the header section options including LDMS, Enterprise Tracking, and Monitoring &amp; Analysis.</t>
-  </si>
-  <si>
-    <t>Worked on TMS, including the header section sub-options such as Dashboard (with its sub-options), Resource Centre sub-options, and the Login button UI, along with improving responsiveness</t>
-  </si>
-  <si>
-    <t>Worked on the TMS Dashboard UI by adding graph charts for analytics, designing card components, and improving the overall dashboard structure</t>
   </si>
   <si>
     <t xml:space="preserve">Worked on the UI part of the TMS home page including all the homepage sections </t>
@@ -325,6 +265,36 @@
 Developed and integrated new fields including dependent dropdowns, multi-selects, and conditional inputs with proper state management.
 Implemented smooth frontend interactions with live validation and consistent data binding for better user experience.
 Conducted thorough testing, debugging, and performance optimization to ensure stable and efficient form functionality.</t>
+  </si>
+  <si>
+    <t>Ongoing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10th feb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ongoing </t>
+  </si>
+  <si>
+    <t>ongoing</t>
+  </si>
+  <si>
+    <t>28th feb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked on Pragati Setu home page UI along with responsoveness </t>
+  </si>
+  <si>
+    <t>Worked on the Pragati Setu, including the header section, the About Us page and its subpages, the Our Services section and its subpages, Beneficiary Profiling, and User Management, while also improving their responsiveness.</t>
+  </si>
+  <si>
+    <t>Worked on Pragati Setu, focusing on the header section options including LDMS, Enterprise Tracking, and Monitoring &amp; Analysis.</t>
+  </si>
+  <si>
+    <t>Worked on Pragati Setu, including the header section sub-options such as Dashboard (with its sub-options), Resource Centre sub-options, and the Login button UI, along with improving responsiveness</t>
+  </si>
+  <si>
+    <t>Worked on the Pragati Setu Dashboard UI by adding graph charts for analytics, designing card components, and improving the overall dashboard structure</t>
   </si>
 </sst>
 </file>
@@ -464,6 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -482,7 +453,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,21 +771,21 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>11</v>
@@ -838,7 +808,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>11</v>
@@ -861,22 +831,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -884,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>11</v>
@@ -899,43 +869,43 @@
         <v>10</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="B7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -943,22 +913,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -966,22 +936,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -989,22 +959,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="F11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1012,22 +982,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.3">
@@ -1035,22 +1005,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
@@ -1058,71 +1028,71 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="B15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
+      <c r="B16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
@@ -1130,22 +1100,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
@@ -1153,22 +1123,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
         <v>48</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
@@ -1176,22 +1146,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
@@ -1199,22 +1169,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
@@ -1222,173 +1192,173 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+      <c r="B23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="15">
+      <c r="A25" s="9">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="9">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="15">
+      <c r="A27" s="9">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="9">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="15">
+      <c r="A29" s="9">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
